--- a/artfynd/A 40970-2021 artfynd.xlsx
+++ b/artfynd/A 40970-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40970-2021 artfynd.xlsx
+++ b/artfynd/A 40970-2021 artfynd.xlsx
@@ -1419,11 +1419,11 @@
         <v>70480356</v>
       </c>
       <c r="B8" t="n">
-        <v>81972</v>
+        <v>83201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545975.1467062032</v>
+        <v>545975</v>
       </c>
       <c r="R8" t="n">
-        <v>6475779.489013081</v>
+        <v>6475779</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1499,19 +1499,9 @@
           <t>2018-03-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-03-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 40970-2021 artfynd.xlsx
+++ b/artfynd/A 40970-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58105648</v>
+        <v>58098717</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>381</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Stor vårtrattskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Rhizocybe vermicularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Fr.) Vizzini &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Linghem, syd - Obj 1335, Ög</t>
+          <t>Linghem, syd - Obj 1337, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545941.8560387299</v>
+        <v>545948</v>
       </c>
       <c r="R2" t="n">
-        <v>6475933.626807213</v>
+        <v>6475867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,14 @@
           <t>2016-03-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-03-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granskog med enstaka tallar i Fågelsångsskogen</t>
+          <t>Barrskog i Fågelsångsskogen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,60 +790,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64150143</v>
+        <v>68304405</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Linghem, Ög</t>
+          <t>Linghemsskogen - Obj 1335, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545951.8193499198</v>
+        <v>545913</v>
       </c>
       <c r="R3" t="n">
-        <v>6475934.267155512</v>
+        <v>6475948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,22 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Granskog med lövinslag som delvis är kalkbarrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,34 +880,43 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>RGC17-063</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64149900</v>
+        <v>58098716</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -963,25 +939,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>S Linghem, Ög</t>
+          <t>Linghem, syd - Obj 1337, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545956.167950841</v>
+        <v>545948</v>
       </c>
       <c r="R4" t="n">
-        <v>6475966.270364461</v>
+        <v>6475867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,22 +978,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barrskog i Fågelsångsskogen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,69 +997,76 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68304651</v>
+        <v>58098859</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linghemsskogen - Obj 1337, Ög</t>
+          <t>Linghem, syd - Obj 1337, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545997.2370099225</v>
+        <v>545961</v>
       </c>
       <c r="R5" t="n">
-        <v>6475730.507124775</v>
+        <v>6475860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,27 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+          <t>Barrskog i Fågelsångsskogen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,9 +1112,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1162,7 +1128,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1173,50 +1139,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68304660</v>
+        <v>58098860</v>
       </c>
       <c r="B6" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1988</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linghemsskogen - Obj 1337, Ög</t>
+          <t>Linghem, syd - Obj 1337, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545997.2370099225</v>
+        <v>545957</v>
       </c>
       <c r="R6" t="n">
-        <v>6475730.507124775</v>
+        <v>6475859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,27 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+          <t>Barrskog i Fågelsångsskogen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,6 +1229,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1283,7 +1243,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1294,50 +1254,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68305572</v>
+        <v>58098861</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linghemsskogen - Obj 1337, Ög</t>
+          <t>Linghem, syd - Obj 1337, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545983.9347240536</v>
+        <v>545977</v>
       </c>
       <c r="R7" t="n">
-        <v>6475746.06650772</v>
+        <v>6475833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,27 +1323,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+          <t>Barrskog i Fågelsångsskogen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,9 +1342,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,7 +1358,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1416,19 +1369,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70480356</v>
+        <v>58105648</v>
       </c>
       <c r="B8" t="n">
-        <v>83222</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1451,28 +1399,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kråksångsskogen, Linghem, Linköping, Linghem, Ög</t>
+          <t>Linghem, syd - Obj 1335, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545975</v>
+        <v>545942</v>
       </c>
       <c r="R8" t="n">
-        <v>6475779</v>
+        <v>6475934</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,12 +1438,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-03-27</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-03-27</t>
+          <t>2016-03-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Granskog med enstaka tallar i Fågelsångsskogen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,72 +1457,85 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janne Moberg</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janne Moberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68617351</v>
+        <v>64149900</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linghemsskogen - Obj 1337, Ög</t>
+          <t>S Linghem, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546000.2504902979</v>
+        <v>545956</v>
       </c>
       <c r="R9" t="n">
-        <v>6475742.066832162</v>
+        <v>6475966</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,27 +1559,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre barrskog med inslag av löv</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,21 +1573,1960 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>64150143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>S Linghem, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>545952</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6475934</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>70480356</v>
+      </c>
+      <c r="B11" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kråksångsskogen, Linghem, Linköping, Linghem, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545975</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6475779</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-03-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-03-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Janne Moberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Janne Moberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>71470027</v>
+      </c>
+      <c r="B12" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Linghem, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545962</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6475846</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-04-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-04-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>76804580</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Linghem motionsspåret, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>545974</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6475844</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2007-04-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2007-04-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Linköpings svampklubb exkursion</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>68304660</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>545997</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6475731</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>68304663</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>546006</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6475759</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>68383383</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1338, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>546020</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6475636</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barrskog som delvis är kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>68304662</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93014</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2055</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Olivinkremla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Russula olivina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ruots. &amp; Vauras</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>546006</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6475759</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>68383384</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93014</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2055</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Olivinkremla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Russula olivina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ruots. &amp; Vauras</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1338, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>546020</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6475636</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barrskog som delvis är kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>68304285</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87412</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1335, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545921</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6475942</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Granskog med lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>68304286</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1335, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>545921</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6475942</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Granskog med lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>68304651</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>545997</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6475731</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>68305572</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>545984</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6475746</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>68617352</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>546000</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6475742</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Rolf-Göran Carlsson, Tomas Fasth</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>68306025</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>545982</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6475650</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>68617349</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1338, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>545946</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6475684</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>68304661</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>546005</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6475760</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Granskog med tall och lövinslag som delvis är kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>68617351</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Linghemsskogen - Obj 1337, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>546000</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6475742</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vårdsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>

--- a/artfynd/A 40970-2021 artfynd.xlsx
+++ b/artfynd/A 40970-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58098717</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58098716</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58098859</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58098860</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58098861</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58105648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,6 +1629,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64149900</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64150143</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70480356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71470027</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76804580</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304660</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304663</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2332,6 +2407,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68383383</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2438,6 +2518,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304662</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2544,6 +2629,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68383384</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2646,6 +2736,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304285</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304286</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2869,6 +2969,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304651</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2976,6 +3081,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68305572</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3082,6 +3192,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68617352</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68306025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3319,6 +3439,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68617349</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3425,6 +3550,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68304661</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3531,8 +3661,41 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68617351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>